--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>466900</v>
+      </c>
+      <c r="E8" s="3">
         <v>492300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>500900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>445400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>422600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>425700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>441400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>405700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>431900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>392100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>386400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>314500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>337300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>330300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>294400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>347200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>342400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>371100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>385700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>355800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>378600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>405300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>434400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>366200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>335300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>355000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>358400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>323300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>317700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>269000</v>
+      </c>
+      <c r="E9" s="3">
         <v>283300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>289400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>261300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>266300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>273700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>288800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>268200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>292000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>252800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>250600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>208700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>227300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>220600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>196200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>220800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>224600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>236500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>252500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>238500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>264200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>284500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>299200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>261800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>234500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>247400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>246400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>227300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>226700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>197900</v>
+      </c>
+      <c r="E10" s="3">
         <v>209000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>211500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>184100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>156300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>152000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>152600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>137500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>139900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>139300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>135800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>105800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>110000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>109700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>98200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>126400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>117800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>134600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>133200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>117300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>114400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>120800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>135200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>104400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>100800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>107600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>112000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>96000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>91000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,35 +1298,38 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-85200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1318,37 +1337,37 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-8100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-8300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>24900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>8100</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1356,12 +1375,12 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>2000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1369,13 +1388,16 @@
         <v>0</v>
       </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>30000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>399800</v>
+      </c>
+      <c r="E17" s="3">
         <v>444400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>425500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>382900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>380100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>374400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>307100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>355500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>373000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>332600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>322800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>241700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>291200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>276800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>280600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>322600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>305200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>347800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>361800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>330400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>361900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>376400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>390700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>351900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>326100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>330400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>325700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>318900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>334700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E18" s="3">
         <v>47900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>75400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>62500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>42500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>51300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>134300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>50200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>58900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>59500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>63600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>72800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>46100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>53500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>24600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>23300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>23900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>25400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>43700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>14300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>32700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1747,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>8600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>57400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-27700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>4500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-23300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>51200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-12000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>30200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>36400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-12200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E21" s="3">
         <v>71200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>86100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>76000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>113400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>67600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>149100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>36600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>90400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>53100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>83200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>64600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>113800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>70800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>37600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>71800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>78200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>45000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>27400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>51100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>19100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>26100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>49700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>21000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E22" s="3">
         <v>26500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>24200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>6500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>9500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>13500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>6300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>4400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E23" s="3">
         <v>30000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>48100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>43400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>84400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>45000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>129300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>16800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>67800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>31200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>60000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>41800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>88400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>45000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>39300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>45900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>19600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>26100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>14600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>13500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-1000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-16900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>24100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E26" s="3">
         <v>31000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>63500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>66700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>89900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>24800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>27200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>60300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>25600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>10400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-15400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E27" s="3">
         <v>25600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>59200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>73000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>36300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>92100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>28900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>22300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>27100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>53000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>82900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>34400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-36600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>24000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>19800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-30500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>13000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>11300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2557,8 +2617,8 @@
       <c r="F29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3">
-        <v>0</v>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H29" s="3">
         <v>0</v>
@@ -2566,59 +2626,59 @@
       <c r="I29" s="3">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
       <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
         <v>100</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>15100</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-1300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-49400</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-47600</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-26500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-2900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-4100</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2629,14 +2689,17 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-57400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>27700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-4500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>23300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-51200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>12000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-30200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-36400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>23100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>12200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>13900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E33" s="3">
         <v>25600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>59200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>73000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>36300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>92100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>28900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>22300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>27200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>53000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>98000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-86000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-35500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>15700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-30500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>13000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>11300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E35" s="3">
         <v>25600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>59200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>73000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>36300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>92100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>28900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>22300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>27200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>53000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>98000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-86000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-35500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>15700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-30500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>13000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>11300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>577900</v>
+      </c>
+      <c r="E41" s="3">
         <v>562100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>353200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>305100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>234400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>361500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>201600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>201400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>325400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>200200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>135800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>141300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>107100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>395800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>137900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>206200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>212300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>334900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>289000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>324800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>322800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>418800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>296100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>337800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>382300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>450100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3480,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O42" s="3">
         <v>100</v>
@@ -3489,699 +3578,723 @@
         <v>100</v>
       </c>
       <c r="Q42" s="3">
+        <v>100</v>
+      </c>
+      <c r="R42" s="3">
         <v>200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>15100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>58300</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>46200</v>
       </c>
       <c r="AC42" s="3">
         <v>46200</v>
       </c>
       <c r="AD42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="AE42" s="3">
         <v>60000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>53700</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1804500</v>
+      </c>
+      <c r="E43" s="3">
         <v>1682900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1689500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1525400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1328500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1102700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1022800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>846500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>726400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>710300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>616900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>529100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>472300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>479200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>488300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>580200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>720500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>725500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>661500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>575900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>551900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>496000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>491000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>421400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>371100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>431300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>358900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>300300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>254500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>202300</v>
+      </c>
+      <c r="E44" s="3">
         <v>214800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>224100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>220900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>214100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>210900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>212700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>197000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>184300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>169700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>157900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>151600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>137100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>149600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>143900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>153100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>148500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>160700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>163300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>166600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>158900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>164500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>158600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>160500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>142600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>140200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>131300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>129300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>119200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E45" s="3">
         <v>37900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>30800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>37300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>121600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>48000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>45900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>56200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>58100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>39600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>82800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>40400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>50400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>78100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>42600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>42500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>37800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>36000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>36500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>39900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>38100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2627400</v>
+      </c>
+      <c r="E46" s="3">
         <v>2497900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2304900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2082200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1805200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1712400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1475500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1366500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1284100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1058600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1050400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>937200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>803300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>809800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>771700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1159000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1089900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1039800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1072700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1007000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1092300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>998400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1021000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>962300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>949800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>910700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>911900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>915500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>427300</v>
+      </c>
+      <c r="E47" s="3">
         <v>514500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>702600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>801500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>732900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>682700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>700600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>639900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>772500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1002800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2229100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2823700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2474300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2509000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2465400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>410100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>472000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>512200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>512700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>462200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>422400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>457900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>451800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>381000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>324000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>286100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>211900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>205400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>182300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>330700</v>
+      </c>
+      <c r="E48" s="3">
         <v>323200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>322000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>289800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>281200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>273900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>264200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>260600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>271600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>242000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>247300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>250400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>258700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>261700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>269900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>279200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>284500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>330500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>336200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>337700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>297500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>296900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>301000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>302600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>272000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>266600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>264400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>254100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>261400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E49" s="3">
         <v>267000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>271400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>217300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>220600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>223700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>223100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>226500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>267800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>272400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>276900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>281400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>289400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>295600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>300600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>305700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>308200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>316800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>365100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>362400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>367500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>380900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>387800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>396300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>369400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>376700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>382500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>386900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>394600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>342000</v>
+      </c>
+      <c r="E52" s="3">
         <v>348700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>166000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>162000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>195900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>175900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>188500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>92400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>79100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>57600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>64500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>93000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>108600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>121400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>139600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>154000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>247900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>146400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>172700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>184100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>176400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>180300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>180100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>178300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>170100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>216300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>222300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>216100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>213300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3990400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3951200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3766900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3552900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3235800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3068600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2852000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2585900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2675200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2633400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3868200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4385900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3934400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3997500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3947000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2308000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2331800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2345700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2459400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2353300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2356100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2314300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2341600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4717,551 +4847,569 @@
         <v>131900</v>
       </c>
       <c r="E57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="F57" s="3">
         <v>135900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>120100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>109600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>132800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>142200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>154500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>123300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>133000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>130500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>136400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>100800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>117000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>107900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>103500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>88200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>107100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>113800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>126500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>106300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>118000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>125200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>123700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>104900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>112300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>104400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>96200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>89300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>10800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>14000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>30800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>17100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>16900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>15400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>3900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>102800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>58600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>53600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>64300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1933100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1955700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1839100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1746400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1538800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1311900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1026400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>627000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>590600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>418700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>391700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>454700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>405500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>434500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>524500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>684200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>950700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>866600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>789700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>588300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>586600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>492500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>442200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>401100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>407900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>316500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>293800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>279000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>312100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2065100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2087800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1975400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1867500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1649100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1445200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1169900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>783000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>715000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>562900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>533000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>602300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>517000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>565600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>646800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>802300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>935800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>990800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>920400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>730200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>696800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>613500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>570900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>528200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>514900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>531600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>456800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>428700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>465800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>361300</v>
+      </c>
+      <c r="E61" s="3">
         <v>361500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>364100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>366800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>373500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>388000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>445000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>634200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>753400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1069500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2399800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2898700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2560500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2594600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2528400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>694000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>471800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>555400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>595300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>622900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>658400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>659500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>672800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>643900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>589100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>338300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>394400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>409200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>330100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>558600</v>
+      </c>
+      <c r="E62" s="3">
         <v>567000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>511500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>498700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>411700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>487700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>513600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>514500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>537800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>396000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>342900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>292100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>317600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>367700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>342500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>382100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>457500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>281800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>421300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>469900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>529300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>506800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>542600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>489900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>493000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>481500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>468200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>476900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>467000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3031800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3065700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2900600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2734200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2435600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2322100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2129500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1932700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2011900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2033600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3280900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3798100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3399700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3532400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3522000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1882500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1868900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1831800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1940700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1826700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1867300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1780800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1793000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,8 +6200,11 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6122,8 +6295,11 @@
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>958600</v>
+      </c>
+      <c r="E76" s="3">
         <v>885500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>866300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>818600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>800200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>746500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>722500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>653200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>663300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>599800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>587400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>587800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>534700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>465100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>425100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>425500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>462800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>513900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>518800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>526600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>488800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>533600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>548600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>536900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>546100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>663200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>595700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>589000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>548700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E81" s="3">
         <v>25600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>59200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>73000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>36300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>92100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>28900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>22300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>27200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>53000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>98000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-86000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-35500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>15700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-30500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>13000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>11300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E83" s="3">
         <v>14700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>12900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>15100</v>
       </c>
       <c r="N83" s="3">
         <v>15100</v>
       </c>
       <c r="O83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="P83" s="3">
         <v>16600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>16300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>16200</v>
       </c>
       <c r="R83" s="3">
         <v>16200</v>
       </c>
       <c r="S83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="T83" s="3">
         <v>18500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>18400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>17900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>19600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>18700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>17700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>18500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>18300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>24100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E89" s="3">
         <v>66200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-48200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-151700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>42300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-87600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-13300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>43900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>93600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>164700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>57200</v>
-      </c>
-      <c r="T89" s="3">
-        <v>8900</v>
       </c>
       <c r="U89" s="3">
         <v>8900</v>
       </c>
       <c r="V89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="W89" s="3">
         <v>36700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>15100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>42800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>81000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>73900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-10700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-24800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>10100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-154000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-90900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-58300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>35500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>176700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1125400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>569100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-354000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>111200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-8400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-117900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-77800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-59500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-67200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-121400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>2700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7969,16 +8202,19 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="E100" s="3">
         <v>168200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>45500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>272700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>115200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>175000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>152800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-145900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-552100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>411800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-143100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1621100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>48200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-93300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>89700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-80700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>87700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>108800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>40000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>127600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>45600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>46200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
       </c>
       <c r="Q101" s="3">
         <v>100</v>
       </c>
       <c r="R101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>500</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>-400</v>
       </c>
       <c r="AF101" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E102" s="3">
         <v>209000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>48100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>70600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-127100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>159900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-123900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>192600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-91600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>24100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>64500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>34200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-288700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>256400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>36200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-94000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-20200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-120900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>43800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-34800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>123900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>121800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-39100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>476300</v>
+      </c>
+      <c r="E8" s="3">
         <v>466900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>492300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>500900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>445400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>422600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>425700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>441400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>405700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>431900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>392100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>386400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>314500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>337300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>330300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>294400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>347200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>342400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>371100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>385700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>355800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>378600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>405300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>434400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>366200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>335300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>355000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>358400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>323300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>317700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>274200</v>
+      </c>
+      <c r="E9" s="3">
         <v>269000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>283300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>289400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>261300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>266300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>273700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>288800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>268200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>292000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>252800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>250600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>208700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>227300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>220600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>196200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>220800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>224600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>236500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>252500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>238500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>264200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>284500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>299200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>261800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>234500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>247400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>246400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>227300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>226700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>202100</v>
+      </c>
+      <c r="E10" s="3">
         <v>197900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>209000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>211500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>184100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>156300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>152000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>152600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>137500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>139900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>139300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>135800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>105800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>110000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>109700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>98200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>126400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>117800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>134600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>133200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>117300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>114400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>120800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>135200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>104400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>100800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>107600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>112000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>96000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>91000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,38 +1318,41 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-85200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1340,37 +1360,37 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-8100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-8300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>24900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>8100</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1378,12 +1398,12 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1391,13 +1411,16 @@
         <v>0</v>
       </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>30000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>409400</v>
+      </c>
+      <c r="E17" s="3">
         <v>399800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>444400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>425500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>382900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>380100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>374400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>307100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>355500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>373000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>332600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>322800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>241700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>291200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>276800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>280600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>322600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>305200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>347800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>361800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>330400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>361900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>376400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>390700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>351900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>326100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>330400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>325700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>318900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>334700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E18" s="3">
         <v>67100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>47900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>75400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>62500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>42500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>51300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>134300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>50200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>58900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>59500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>63600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>72800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>46100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>53500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>24600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>23300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>25400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>43700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>14300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,483 +1781,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>57400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-27700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-21400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-23300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>51200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-18000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-12000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>30200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>36400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-14400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E21" s="3">
         <v>83200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>71200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>86100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>76000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>113400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>67600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>149100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>36600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>90400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>53100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>83200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>64600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>113800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>70800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>37600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>71800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>78200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>45000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>27400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>51100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>19100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>26100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>43300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>49700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>21000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E22" s="3">
         <v>28400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>26500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>9500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>21600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>11900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>6300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>4400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>45700</v>
+      </c>
+      <c r="E23" s="3">
         <v>39700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>48100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>43400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>84400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>45000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>129300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>16800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>67800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>60000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>41800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>88400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>45000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>39300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>45900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>26100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>39400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>13500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-16900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>14800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>24100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>10400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E26" s="3">
         <v>39600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>63500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>28800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>66700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>35800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>89900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>40200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>24800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>27200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>60300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>25600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-15400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>12000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E27" s="3">
         <v>41300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>59200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>73000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>36300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>92100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>28900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>22300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>27100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>53000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>82900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>34400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-36600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>24000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>19800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>13000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>11300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2620,8 +2681,8 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>0</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2629,59 +2690,59 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>100</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>15100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-1300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-49400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-47600</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-26500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-2900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-4100</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2692,14 +2753,17 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-57400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>27700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>21400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>23300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-51200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>18000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>12000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-30200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-36400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>14400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>23100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>12200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>13900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E33" s="3">
         <v>41300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>59200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>73000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>36300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>92100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>28900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>22300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>27200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>53000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>98000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-86000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-35500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>21100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>15700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>13000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>11300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E35" s="3">
         <v>41300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>59200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>73000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>36300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>92100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>28900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>22300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>27200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>53000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>98000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-86000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-35500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>21100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>15700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>13000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>11300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>446700</v>
+      </c>
+      <c r="E41" s="3">
         <v>577900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>562100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>353200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>305100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>234400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>361500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>201600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>201400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>325400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>224300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>200200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>135800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>141300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>107100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>395800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>137900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>112100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>206200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>212300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>334900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>289000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>324800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>322800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>418800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>296100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>337800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>382300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>450100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3572,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P42" s="3">
         <v>100</v>
@@ -3581,720 +3671,744 @@
         <v>100</v>
       </c>
       <c r="R42" s="3">
+        <v>100</v>
+      </c>
+      <c r="S42" s="3">
         <v>200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>15100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>58300</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>46200</v>
       </c>
       <c r="AD42" s="3">
         <v>46200</v>
       </c>
       <c r="AE42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="AF42" s="3">
         <v>60000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>53700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1630200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1804500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1682900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1689500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1525400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1328500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1102700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1022800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>846500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>726400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>710300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>616900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>529100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>472300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>479200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>488300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>580200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>720500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>725500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>661500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>575900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>551900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>496000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>491000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>421400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>371100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>431300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>358900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>300300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>254500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>204800</v>
+      </c>
+      <c r="E44" s="3">
         <v>202300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>214800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>224100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>220900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>214100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>210900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>212700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>197000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>184300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>169700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>157900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>151600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>137100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>143900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>153100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>148500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>160700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>163300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>166600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>158900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>164500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>158600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>160500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>142600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>140200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>131300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>129300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>119200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E45" s="3">
         <v>42600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>37900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>30800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>37300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>121600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>48000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>45900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>56200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>39600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>82800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>50400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>78100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>45700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>42600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>37800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>36000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>36500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>39900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>38100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2313200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2627400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2497900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2304900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2082200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1805200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1712400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1475500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1366500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1284100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1058600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1050400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>937200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>803300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>809800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>771700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1159000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1089900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1039800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1072700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1007000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1092300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>998400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1021000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>962300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>949800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>910700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>911900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>915500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>406800</v>
+      </c>
+      <c r="E47" s="3">
         <v>427300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>514500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>702600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>801500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>732900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>682700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>700600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>639900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>772500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1002800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2229100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2823700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2474300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2509000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2465400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>410100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>472000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>512200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>512700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>462200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>422400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>457900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>451800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>381000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>324000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>286100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>211900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>205400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>182300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>325800</v>
+      </c>
+      <c r="E48" s="3">
         <v>330700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>323200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>322000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>289800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>281200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>273900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>264200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>260600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>271600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>242000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>247300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>250400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>258700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>261700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>269900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>279200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>284500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>330500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>336200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>337700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>297500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>296900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>301000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>302600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>272000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>266600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>264400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>254100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>261400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>258600</v>
+      </c>
+      <c r="E49" s="3">
         <v>263000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>267000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>271400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>217300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>220600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>223700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>223100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>226500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>267800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>272400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>276900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>281400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>289400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>295600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>300600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>305700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>308200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>316800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>365100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>362400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>367500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>380900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>387800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>396300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>369400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>376700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>382500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>386900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>394600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>336500</v>
+      </c>
+      <c r="E52" s="3">
         <v>342000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>348700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>166000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>162000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>195900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>175900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>188500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>92400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>79100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>57600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>64500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>93000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>108600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>121400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>139600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>154000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>247900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>146400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>172700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>184100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>176400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>180300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>180100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>178300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>170100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>216300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>222300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>216100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>213300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3641000</v>
+      </c>
+      <c r="E54" s="3">
         <v>3990400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3951200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3766900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3552900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3235800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3068600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2852000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2585900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2675200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2633400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3868200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4385900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3934400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3997500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3947000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2308000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2331800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2345700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2459400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2353300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2356100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2314300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2341600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>131900</v>
+        <v>142900</v>
       </c>
       <c r="E57" s="3">
         <v>131900</v>
       </c>
       <c r="F57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="G57" s="3">
         <v>135900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>120100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>109600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>132800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>142200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>154500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>123300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>133000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>130500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>136400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>100800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>117000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>107900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>103500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>88200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>107100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>113800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>126500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>106300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>118000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>125200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>123700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>104900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>112300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>104400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>96200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>89300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4942,474 +5076,489 @@
         <v>100</v>
       </c>
       <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
         <v>300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>30800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>17100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>16900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>15400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>102800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>58600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>53600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>64300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1933100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1955700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1839100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1746400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1538800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1311900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1026400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>627000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>590600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>418700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>391700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>454700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>405500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>434500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>524500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>684200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>950700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>866600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>789700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>588300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>586600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>492500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>442200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>401100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>407900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>316500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>293800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>279000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>312100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1864900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2065100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2087800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1975400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1867500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1649100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1445200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1169900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>783000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>715000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>562900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>533000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>602300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>517000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>565600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>646800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>802300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>935800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>990800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>920400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>730200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>696800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>613500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>570900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>528200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>514900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>531600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>456800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>428700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>465800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>254900</v>
+      </c>
+      <c r="E61" s="3">
         <v>361300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>361500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>364100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>366800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>373500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>388000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>445000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>634200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>753400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1069500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2399800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2898700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2560500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2594600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2528400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>694000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>471800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>555400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>595300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>622900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>658400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>659500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>672800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>643900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>589100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>338300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>394400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>409200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>330100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>519900</v>
+      </c>
+      <c r="E62" s="3">
         <v>558600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>567000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>511500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>498700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>411700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>487700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>513600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>514500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>537800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>396000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>342900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>292100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>317600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>367700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>342500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>382100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>457500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>281800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>421300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>469900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>529300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>506800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>542600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>489900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>493000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>481500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>468200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>476900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>467000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2687300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3031800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3065700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2900600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2734200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2435600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2322100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2129500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1932700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2011900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2033600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3280900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3798100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3399700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3532400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3522000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1882500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1868900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1831800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1940700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1826700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1867300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1780800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1793000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,8 +6374,11 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6298,8 +6472,11 @@
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>953700</v>
+      </c>
+      <c r="E76" s="3">
         <v>958600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>885500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>866300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>818600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>800200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>746500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>722500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>653200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>663300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>599800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>587400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>587800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>534700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>465100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>425100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>425500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>462800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>513900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>518800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>526600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>488800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>533600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>548600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>536900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>546100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>663200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>595700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>589000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>548700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34200</v>
+      </c>
+      <c r="E81" s="3">
         <v>41300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>59200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>73000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>36300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>92100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>28900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>22300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>27200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>53000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>98000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-86000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-35500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>21100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>15700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-30500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>13000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>11300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E83" s="3">
         <v>15100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>13800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>12900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>13500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>13300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>14200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>15300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>15100</v>
       </c>
       <c r="O83" s="3">
         <v>15100</v>
       </c>
       <c r="P83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="Q83" s="3">
         <v>16600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>16300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>16200</v>
       </c>
       <c r="S83" s="3">
         <v>16200</v>
       </c>
       <c r="T83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="U83" s="3">
         <v>18500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>18400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>17900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>19600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>18700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>17700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>24100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>197500</v>
+      </c>
+      <c r="E89" s="3">
         <v>9500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>66200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-48200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-151700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>42300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-87600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-13300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>43900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>36400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>93600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>164700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>57200</v>
-      </c>
-      <c r="U89" s="3">
-        <v>8900</v>
       </c>
       <c r="V89" s="3">
         <v>8900</v>
       </c>
       <c r="W89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="X89" s="3">
         <v>36700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>15100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>42800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>81000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>73900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-10700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E94" s="3">
         <v>26500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-24800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>10100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-154000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-90900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-58300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>35500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>176700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1125400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>569100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-354000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>111200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-69300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-117900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-77800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-59500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-67200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8205,16 +8439,19 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-367300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-21900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>168200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>272700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>115200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>175000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>152800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-145900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-552100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>411800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-143100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1621100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>48200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-93300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>89700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-80700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>87700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>108800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>40000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>127600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>45600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>46200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>100</v>
       </c>
       <c r="R101" s="3">
         <v>100</v>
       </c>
       <c r="S101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>500</v>
-      </c>
-      <c r="AF101" s="3">
-        <v>-400</v>
       </c>
       <c r="AG101" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-131300</v>
+      </c>
+      <c r="E102" s="3">
         <v>15800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>209000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>48100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>70600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-127100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>159900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-123900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>192600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-91600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>64500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>34200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-288700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>256400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>36200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-94000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-20200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-120900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-34800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>123900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>121800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-39100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>533200</v>
+      </c>
+      <c r="E8" s="3">
         <v>476300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>466900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>492300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>500900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>445400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>422600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>425700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>441400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>405700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>431900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>392100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>386400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>314500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>337300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>330300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>294400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>347200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>342400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>371100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>385700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>355800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>378600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>405300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>434400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>366200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>335300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>355000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>358400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>323300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>317700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>303200</v>
+      </c>
+      <c r="E9" s="3">
         <v>274200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>269000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>283300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>289400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>261300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>266300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>273700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>288800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>268200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>292000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>252800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>250600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>208700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>227300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>220600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>196200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>220800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>224600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>236500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>252500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>238500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>264200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>284500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>299200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>261800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>234500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>247400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>246400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>227300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>226700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>230000</v>
+      </c>
+      <c r="E10" s="3">
         <v>202100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>197900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>209000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>211500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>184100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>156300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>152000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>137500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>139900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>139300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>135800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>105800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>110000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>109700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>98200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>126400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>117800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>134600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>133200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>117300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>114400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>120800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>135200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>104400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>100800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>107600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>112000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>96000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>91000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,41 +1338,44 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-85200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1363,37 +1383,37 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-8300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>24900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>8100</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1401,12 +1421,12 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>2000</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1414,13 +1434,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>30000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>443400</v>
+      </c>
+      <c r="E17" s="3">
         <v>409400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>399800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>444400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>425500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>382900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>380100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>374400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>307100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>355500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>373000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>332600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>322800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>241700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>291200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>276800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>280600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>322600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>305200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>347800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>361800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>330400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>361900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>376400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>390700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>351900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>326100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>330400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>325700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>318900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>334700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E18" s="3">
         <v>66900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>67100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>47900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>75400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>62500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>42500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>51300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>134300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>50200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>58900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>59500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>63600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>72800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>46100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>53500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>23300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>25400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>28900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>43700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,498 +1815,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>900</v>
+      </c>
+      <c r="E20" s="3">
         <v>4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>57400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-27700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>16100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>51200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-12000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>36400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-14400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E21" s="3">
         <v>85400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>83200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>71200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>86100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>76000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>113400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>67600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>149100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>36600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>90400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>53100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>83200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>64600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>113800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>70800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>37600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>71800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>78200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>45000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>27400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>51100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>19100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>26100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>43300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>49700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>21000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E22" s="3">
         <v>25400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>26500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>9500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>21600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>6300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E23" s="3">
         <v>45700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>30000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>43400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>84400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>45000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>129300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>16800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>67800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>60000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>41800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>88400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>45000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>39300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>45900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>19600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>18500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>26100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="E24" s="3">
         <v>10900</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-15300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>17700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>39400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>35400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>13500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-16900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>13700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>14800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>24100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>9900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>10400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E26" s="3">
         <v>34800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>39600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>31000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>63500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>28800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>66700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>89900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>9200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>40200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>24800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>27200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>60300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>20500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>25600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-15400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E27" s="3">
         <v>34200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>41300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>59200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>73000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>36300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>92100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>28900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>22300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>27100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>53000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>82900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>34400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-36600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>24000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>19800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>13000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>11300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2684,8 +2745,8 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2693,59 +2754,59 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>100</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>15100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-1300</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-49400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-47600</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-26500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-2900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-4100</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2756,14 +2817,17 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-57400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>27700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-16100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>23300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-51200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>12000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-36400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>14400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>23100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>12200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>13900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E33" s="3">
         <v>34200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>41300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>59200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>73000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>36300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>92100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>28900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>22300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>27200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>53000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>98000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-86000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-35500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>21100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>15700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>13000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>11300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E35" s="3">
         <v>34200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>41300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>59200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>73000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>36300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>92100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>28900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>22300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>27200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>53000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>98000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-86000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-35500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>21100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>15700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>13000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>11300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>428800</v>
+      </c>
+      <c r="E41" s="3">
         <v>446700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>577900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>562100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>353200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>305100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>234400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>361500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>201600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>201400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>325400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>132700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>135800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>141300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>107100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>395800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>137900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>112100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>206200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>212300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>334900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>289000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>324800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>322800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>418800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>296100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>337800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>382300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>450100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3665,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="3">
         <v>100</v>
@@ -3674,741 +3764,765 @@
         <v>100</v>
       </c>
       <c r="S42" s="3">
+        <v>100</v>
+      </c>
+      <c r="T42" s="3">
         <v>200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1400</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3200</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>15100</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>58300</v>
-      </c>
-      <c r="AD42" s="3">
-        <v>46200</v>
       </c>
       <c r="AE42" s="3">
         <v>46200</v>
       </c>
       <c r="AF42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="AG42" s="3">
         <v>60000</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>53700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1615300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1630200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1804500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1682900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1689500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1525400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1328500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1102700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1022800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>846500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>726400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>710300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>616900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>529100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>472300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>479200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>488300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>580200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>720500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>725500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>661500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>575900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>551900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>496000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>491000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>421400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>371100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>431300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>358900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>300300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>254500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>205400</v>
+      </c>
+      <c r="E44" s="3">
         <v>204800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>202300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>214800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>224100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>220900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>214100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>210900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>212700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>197000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>184300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>169700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>157900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>151600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>137100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>149600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>143900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>153100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>148500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>160700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>163300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>166600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>158900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>164500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>158600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>160500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>142600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>140200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>131300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>129300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>119200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E45" s="3">
         <v>31500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>30800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>28200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>37300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>38400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>121600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>48000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>45900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>56200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>39600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>29800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>40400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>40300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>50400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>78100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>45700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>42500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>37800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>36000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>36500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>39900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>38100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2291800</v>
+      </c>
+      <c r="E46" s="3">
         <v>2313200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2627400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2497900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2304900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2082200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1805200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1712400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1475500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1366500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1284100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1058600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1050400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>937200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>803300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>809800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>771700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1159000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1089900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1039800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1072700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1007000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1092300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>998400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1021000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>962300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>949800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>910700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>911900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>915500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>395600</v>
+      </c>
+      <c r="E47" s="3">
         <v>406800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>427300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>514500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>702600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>801500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>732900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>682700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>700600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>639900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>772500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1002800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2229100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2823700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2474300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2509000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2465400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>410100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>472000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>512200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>512700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>462200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>422400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>457900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>451800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>381000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>324000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>286100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>211900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>205400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>182300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>320000</v>
+      </c>
+      <c r="E48" s="3">
         <v>325800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>330700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>323200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>322000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>289800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>281200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>273900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>264200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>260600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>271600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>242000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>247300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>250400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>258700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>261700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>269900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>279200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>284500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>330500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>336200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>337700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>297500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>296900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>301000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>302600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>272000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>266600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>264400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>254100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>261400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>254400</v>
+      </c>
+      <c r="E49" s="3">
         <v>258600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>263000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>267000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>271400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>217300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>220600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>223700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>223100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>226500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>267800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>272400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>276900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>281400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>289400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>295600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>300600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>305700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>308200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>316800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>365100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>362400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>367500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>380900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>387800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>396300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>369400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>376700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>382500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>386900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>394600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>412900</v>
+      </c>
+      <c r="E52" s="3">
         <v>336500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>342000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>348700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>166000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>162000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>195900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>175900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>188500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>92400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>79100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>57600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>64500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>93000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>108600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>121400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>139600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>154000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>247900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>146400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>172700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>184100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>176400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>180300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>180100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>178300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>170100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>216300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>222300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>216100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>213300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3674700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3641000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3990400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3951200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3766900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3552900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3235800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3068600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2852000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2585900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2675200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2633400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3868200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4385900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3934400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3997500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3947000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2308000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2331800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2345700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2459400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2353300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2356100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2314300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2341600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>151700</v>
+      </c>
+      <c r="E57" s="3">
         <v>142900</v>
-      </c>
-      <c r="E57" s="3">
-        <v>131900</v>
       </c>
       <c r="F57" s="3">
         <v>131900</v>
       </c>
       <c r="G57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="H57" s="3">
         <v>135900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>120100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>109600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>132800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>142200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>154500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>123300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>133000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>130500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>136400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>100800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>117000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>107900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>103500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>88200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>107100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>113800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>126500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>106300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>118000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>125200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>123700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>104900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>112300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>104400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>96200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>89300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5079,486 +5213,501 @@
         <v>100</v>
       </c>
       <c r="F58" s="3">
+        <v>100</v>
+      </c>
+      <c r="G58" s="3">
         <v>300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>11200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>30800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>17100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>15400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>102800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>58600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>53600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>64300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1669100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1722000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1933100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1955700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1839100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1746400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1538800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1311900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1026400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>627000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>590600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>418700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>391700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>454700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>405500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>434500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>524500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>684200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>950700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>866600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>789700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>588300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>586600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>492500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>442200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>401100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>407900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>316500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>293800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>279000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>312100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1820800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1864900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2065100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2087800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1975400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1867500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1649100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1445200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1169900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>783000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>715000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>562900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>533000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>602300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>517000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>565600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>646800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>802300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>935800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>990800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>920400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>730200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>696800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>613500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>570900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>528200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>514900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>531600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>456800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>428700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>465800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>238600</v>
+      </c>
+      <c r="E61" s="3">
         <v>254900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>361300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>361500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>364100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>366800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>373500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>388000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>445000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>634200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>753400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1069500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2399800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2898700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2560500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2594600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2528400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>694000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>471800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>555400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>595300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>622900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>658400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>659500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>672800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>643900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>589100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>338300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>394400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>409200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>330100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>501600</v>
+      </c>
+      <c r="E62" s="3">
         <v>519900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>558600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>567000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>511500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>498700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>411700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>487700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>513600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>514500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>537800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>396000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>342900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>292100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>317600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>367700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>342500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>382100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>457500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>281800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>421300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>469900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>529300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>506800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>542600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>489900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>493000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>481500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>468200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>476900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>467000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2606500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2687300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3031800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3065700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2900600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2734200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2435600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2322100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2129500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1932700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2011900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2033600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3280900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3798100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3399700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3532400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3522000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1882500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1868900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1831800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1940700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1826700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1867300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1780800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1793000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,8 +6548,11 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1068300</v>
+      </c>
+      <c r="E76" s="3">
         <v>953700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>958600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>885500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>866300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>818600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>800200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>746500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>722500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>653200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>663300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>599800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>587400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>587800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>534700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>465100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>425100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>425500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>462800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>513900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>518800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>526600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>488800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>533600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>548600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>536900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>546100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>663200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>595700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>589000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>548700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>116300</v>
+      </c>
+      <c r="E81" s="3">
         <v>34200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>41300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>59200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>73000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>36300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>92100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>28900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>22300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>27200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>53000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>98000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-86000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-35500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>21100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>15700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-30500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>13000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>11300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7211,97 +7410,100 @@
         <v>14400</v>
       </c>
       <c r="E83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="F83" s="3">
         <v>15100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>14700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>13800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>12900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>13500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>14200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>15300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>15100</v>
       </c>
       <c r="P83" s="3">
         <v>15100</v>
       </c>
       <c r="Q83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="R83" s="3">
         <v>16600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>16300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>16200</v>
       </c>
       <c r="T83" s="3">
         <v>16200</v>
       </c>
       <c r="U83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="V83" s="3">
         <v>18500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>18400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>17900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>20400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>18700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>18500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>24100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E89" s="3">
         <v>197500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>66200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-48200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-151700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>42300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-87600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-13300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>18800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>29500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>36400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>93600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>164700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>57200</v>
-      </c>
-      <c r="V89" s="3">
-        <v>8900</v>
       </c>
       <c r="W89" s="3">
         <v>8900</v>
       </c>
       <c r="X89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="Y89" s="3">
         <v>36700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>15100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>42800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>81000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>73900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-14800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-12800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-10700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-10700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E94" s="3">
         <v>39100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>26500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-24800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>10100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-154000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-90900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-58300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>35500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>176700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1125400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>569100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-354000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>111200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-8400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-69300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-10000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-117900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-77800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-59500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-67200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>2700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8442,16 +8676,19 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-103300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-367300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-21900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>168200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>45500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>272700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>115200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>175000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>152800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-145900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-552100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>411800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-143100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1621100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>48200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-93300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>89700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-80700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>87700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>108800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>40000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>127600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>45600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>46200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="R101" s="3">
-        <v>100</v>
       </c>
       <c r="S101" s="3">
         <v>100</v>
       </c>
       <c r="T101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
-      </c>
-      <c r="AG101" s="3">
-        <v>-400</v>
       </c>
       <c r="AH101" s="3">
         <v>-400</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-131300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>209000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>48100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>70600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-127100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>159900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-123900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>192600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-91600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>24100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>64500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>34200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-288700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>256400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>36200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-94000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-20200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-120900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>43800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-34800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>123900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>121800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-39100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>520400</v>
+      </c>
+      <c r="E8" s="3">
         <v>533200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>476300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>466900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>492300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>500900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>445400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>422600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>425700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>441400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>405700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>431900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>392100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>386400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>314500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>337300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>330300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>294400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>347200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>342400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>371100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>385700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>355800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>378600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>405300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>434400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>366200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>335300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>355000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>358400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>323300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>317700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>295600</v>
+      </c>
+      <c r="E9" s="3">
         <v>303200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>274200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>269000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>283300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>289400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>261300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>266300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>273700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>288800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>268200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>292000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>252800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>250600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>208700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>227300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>220600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>196200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>220800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>224600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>236500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>252500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>238500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>264200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>284500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>299200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>261800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>234500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>247400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>246400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>227300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>226700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>230000</v>
+        <v>195100</v>
       </c>
       <c r="E10" s="3">
-        <v>202100</v>
+        <v>204600</v>
       </c>
       <c r="F10" s="3">
-        <v>197900</v>
+        <v>177500</v>
       </c>
       <c r="G10" s="3">
-        <v>209000</v>
+        <v>168100</v>
       </c>
       <c r="H10" s="3">
-        <v>211500</v>
+        <v>149600</v>
       </c>
       <c r="I10" s="3">
-        <v>184100</v>
+        <v>189900</v>
       </c>
       <c r="J10" s="3">
+        <v>162500</v>
+      </c>
+      <c r="K10" s="3">
         <v>156300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>152000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>152600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>137500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>139900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>139300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>135800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>105800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>110000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>109700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>98200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>126400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>117800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>134600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>133200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>117300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>114400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>120800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>135200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>104400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>107600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>112000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>96000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>91000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,44 +1358,47 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+        <v>2600</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-1000</v>
       </c>
       <c r="F14" s="3">
-        <v>500</v>
+        <v>-4100</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H14" s="3">
-        <v>300</v>
+        <v>-8700</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="J14" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-85200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1386,37 +1406,37 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-8100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>1200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-8300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>24900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>8100</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1424,12 +1444,12 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>2000</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1437,36 +1457,39 @@
         <v>0</v>
       </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>30000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>14400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>14400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>15100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>14700</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>12900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1543,8 +1566,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>443400</v>
+        <v>462600</v>
       </c>
       <c r="E17" s="3">
-        <v>409400</v>
+        <v>468300</v>
       </c>
       <c r="F17" s="3">
-        <v>399800</v>
+        <v>434200</v>
       </c>
       <c r="G17" s="3">
-        <v>444400</v>
+        <v>427500</v>
       </c>
       <c r="H17" s="3">
-        <v>425500</v>
+        <v>467600</v>
       </c>
       <c r="I17" s="3">
-        <v>382900</v>
+        <v>447300</v>
       </c>
       <c r="J17" s="3">
+        <v>397800</v>
+      </c>
+      <c r="K17" s="3">
         <v>380100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>374400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>307100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>355500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>373000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>332600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>322800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>241700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>291200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>276800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>280600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>322600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>305200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>347800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>361800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>330400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>361900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>376400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>390700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>351900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>326100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>330400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>325700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>318900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>334700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>89800</v>
+        <v>57800</v>
       </c>
       <c r="E18" s="3">
-        <v>66900</v>
+        <v>64900</v>
       </c>
       <c r="F18" s="3">
-        <v>67100</v>
+        <v>42200</v>
       </c>
       <c r="G18" s="3">
-        <v>47900</v>
+        <v>39400</v>
       </c>
       <c r="H18" s="3">
-        <v>75400</v>
+        <v>24700</v>
       </c>
       <c r="I18" s="3">
-        <v>62500</v>
+        <v>53600</v>
       </c>
       <c r="J18" s="3">
+        <v>47600</v>
+      </c>
+      <c r="K18" s="3">
         <v>42500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>51300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>134300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>50200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>58900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>59500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>63600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>72800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>53500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>37200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>23300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>25400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>28900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>43700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>32700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1849,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>4100</v>
+        <v>-1800</v>
       </c>
       <c r="F20" s="3">
-        <v>900</v>
+        <v>-800</v>
       </c>
       <c r="G20" s="3">
-        <v>8600</v>
+        <v>-5400</v>
       </c>
       <c r="H20" s="3">
-        <v>-3100</v>
+        <v>2300</v>
       </c>
       <c r="I20" s="3">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="J20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K20" s="3">
         <v>57400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-27700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>16100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>4500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-23300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>51200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-18000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-12000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>30200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>36400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-14400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>105200</v>
+        <v>72700</v>
       </c>
       <c r="E21" s="3">
-        <v>85400</v>
+        <v>81100</v>
       </c>
       <c r="F21" s="3">
+        <v>57400</v>
+      </c>
+      <c r="G21" s="3">
+        <v>59900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>37000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>66400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>57700</v>
+      </c>
+      <c r="K21" s="3">
+        <v>113400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>67600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>149100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>36600</v>
+      </c>
+      <c r="O21" s="3">
+        <v>90400</v>
+      </c>
+      <c r="P21" s="3">
+        <v>53100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>83200</v>
       </c>
-      <c r="G21" s="3">
-        <v>71200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>86100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>76000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>113400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>67600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>149100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>36600</v>
-      </c>
-      <c r="N21" s="3">
-        <v>90400</v>
-      </c>
-      <c r="O21" s="3">
-        <v>53100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>83200</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>64600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>113800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>70800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>37600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>71800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>78200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>45000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>22800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>27400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>51100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>19100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>26100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>43300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>49700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>21000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>9900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>24800</v>
+        <v>2000</v>
       </c>
       <c r="E22" s="3">
-        <v>25400</v>
+        <v>1700</v>
       </c>
       <c r="F22" s="3">
-        <v>28400</v>
+        <v>1400</v>
       </c>
       <c r="G22" s="3">
-        <v>26500</v>
+        <v>2500</v>
       </c>
       <c r="H22" s="3">
-        <v>24200</v>
+        <v>4100</v>
       </c>
       <c r="I22" s="3">
-        <v>19700</v>
+        <v>5800</v>
       </c>
       <c r="J22" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K22" s="3">
         <v>15500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>21600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>14200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>13500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>6300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>4400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E23" s="3">
         <v>66000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>45700</v>
       </c>
-      <c r="F23" s="3">
-        <v>39700</v>
-      </c>
       <c r="G23" s="3">
-        <v>30000</v>
+        <v>42700</v>
       </c>
       <c r="H23" s="3">
-        <v>48100</v>
+        <v>26900</v>
       </c>
       <c r="I23" s="3">
-        <v>43400</v>
+        <v>43300</v>
       </c>
       <c r="J23" s="3">
+        <v>39400</v>
+      </c>
+      <c r="K23" s="3">
         <v>84400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>45000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>129300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>16800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>67800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>31200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>60000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>41800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>88400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>45000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>39300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>45900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>19600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>18500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>26100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-59000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>10900</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-15300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>17700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>39400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>13500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-16900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>13700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>14800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>7600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>24100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>10400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E26" s="3">
         <v>124900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34800</v>
       </c>
-      <c r="F26" s="3">
-        <v>39600</v>
-      </c>
       <c r="G26" s="3">
-        <v>31000</v>
+        <v>42700</v>
       </c>
       <c r="H26" s="3">
-        <v>63500</v>
+        <v>27900</v>
       </c>
       <c r="I26" s="3">
-        <v>28800</v>
+        <v>58600</v>
       </c>
       <c r="J26" s="3">
+        <v>24800</v>
+      </c>
+      <c r="K26" s="3">
         <v>66700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>89900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>9200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>24800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>27200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>60300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>20500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>25600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E27" s="3">
         <v>116300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>41300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>25600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>59200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>73000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>36300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>92100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>28900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>22300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>27100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>53000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>82900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>34400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>24000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>19800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>13000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>11300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,91 +2783,94 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>100</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>15100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>1100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-1300</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-49400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-47600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-26500</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-4100</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2820,14 +2881,17 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-900</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-4100</v>
+        <v>1800</v>
       </c>
       <c r="F32" s="3">
-        <v>-900</v>
+        <v>800</v>
       </c>
       <c r="G32" s="3">
-        <v>-8600</v>
+        <v>5400</v>
       </c>
       <c r="H32" s="3">
-        <v>3100</v>
+        <v>-2300</v>
       </c>
       <c r="I32" s="3">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="J32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="K32" s="3">
         <v>-57400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>27700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-16100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>23300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-51200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>18000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>12000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-30200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-36400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>14400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>23100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>12200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>13900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E33" s="3">
         <v>116300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>41300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>25600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>59200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>73000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>36300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>92100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>28900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>22300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>27200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>53000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>98000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-86000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-35500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>21100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>15700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>13000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>11300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E35" s="3">
         <v>116300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>41300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>25600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>59200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>73000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>36300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>92100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>28900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>22300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>27200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>53000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>98000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-86000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-35500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>21100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>15700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>13000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>11300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>388100</v>
+      </c>
+      <c r="E41" s="3">
         <v>428800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>446700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>577900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>562100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>353200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>305100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>234400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>361500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>201600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>201400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>325400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>224300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>135800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>141300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>107100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>395800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>137900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>112100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>206200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>212300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>334900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>289000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>324800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>322800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>418800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>296100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>337800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>382300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>450100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3758,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R42" s="3">
         <v>100</v>
@@ -3767,762 +3857,786 @@
         <v>100</v>
       </c>
       <c r="T42" s="3">
+        <v>100</v>
+      </c>
+      <c r="U42" s="3">
         <v>200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1400</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>15100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>58300</v>
-      </c>
-      <c r="AE42" s="3">
-        <v>46200</v>
       </c>
       <c r="AF42" s="3">
         <v>46200</v>
       </c>
       <c r="AG42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="AH42" s="3">
         <v>60000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>53700</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1615300</v>
+        <v>1024300</v>
       </c>
       <c r="E43" s="3">
-        <v>1630200</v>
+        <v>932200</v>
       </c>
       <c r="F43" s="3">
-        <v>1804500</v>
+        <v>925000</v>
       </c>
       <c r="G43" s="3">
-        <v>1682900</v>
+        <v>935600</v>
       </c>
       <c r="H43" s="3">
-        <v>1689500</v>
+        <v>906900</v>
       </c>
       <c r="I43" s="3">
-        <v>1525400</v>
+        <v>946100</v>
       </c>
       <c r="J43" s="3">
+        <v>830400</v>
+      </c>
+      <c r="K43" s="3">
         <v>1328500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1102700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1022800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>846500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>726400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>710300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>616900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>529100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>472300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>479200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>488300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>580200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>720500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>725500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>661500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>575900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>551900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>496000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>491000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>421400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>371100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>431300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>358900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>300300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>254500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>210700</v>
+      </c>
+      <c r="E44" s="3">
         <v>205400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>204800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>202300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>214800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>224100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>220900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>214100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>210900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>212700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>197000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>184300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>169700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>157900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>151600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>137100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>149600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>143900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>153100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>148500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>160700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>163300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>166600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>158900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>164500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>158600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>160500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>142600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>140200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>131300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>129300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>119200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>42300</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>31500</v>
-      </c>
-      <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
+        <v>100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>0</v>
+      </c>
+      <c r="I45" s="3">
+        <v>100</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>28200</v>
+      </c>
+      <c r="L45" s="3">
+        <v>37300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>38400</v>
+      </c>
+      <c r="N45" s="3">
+        <v>121600</v>
+      </c>
+      <c r="O45" s="3">
+        <v>48000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>45900</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>51300</v>
+      </c>
+      <c r="R45" s="3">
+        <v>56200</v>
+      </c>
+      <c r="S45" s="3">
+        <v>58100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>39600</v>
+      </c>
+      <c r="U45" s="3">
+        <v>32200</v>
+      </c>
+      <c r="V45" s="3">
+        <v>29800</v>
+      </c>
+      <c r="W45" s="3">
+        <v>82800</v>
+      </c>
+      <c r="X45" s="3">
+        <v>40400</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>40300</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>50400</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>78100</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>45700</v>
+      </c>
+      <c r="AC45" s="3">
         <v>42600</v>
       </c>
-      <c r="G45" s="3">
-        <v>37900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>38200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>30800</v>
-      </c>
-      <c r="J45" s="3">
-        <v>28200</v>
-      </c>
-      <c r="K45" s="3">
-        <v>37300</v>
-      </c>
-      <c r="L45" s="3">
-        <v>38400</v>
-      </c>
-      <c r="M45" s="3">
-        <v>121600</v>
-      </c>
-      <c r="N45" s="3">
-        <v>48000</v>
-      </c>
-      <c r="O45" s="3">
-        <v>45900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>51300</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>56200</v>
-      </c>
-      <c r="R45" s="3">
-        <v>58100</v>
-      </c>
-      <c r="S45" s="3">
-        <v>39600</v>
-      </c>
-      <c r="T45" s="3">
-        <v>32200</v>
-      </c>
-      <c r="U45" s="3">
-        <v>29800</v>
-      </c>
-      <c r="V45" s="3">
-        <v>82800</v>
-      </c>
-      <c r="W45" s="3">
-        <v>40400</v>
-      </c>
-      <c r="X45" s="3">
-        <v>40300</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>50400</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>78100</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>45700</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>42600</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>42500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>37800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>36000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>39900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>38100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2317900</v>
+      </c>
+      <c r="E46" s="3">
         <v>2291800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2313200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2627400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2497900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2304900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2082200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1805200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1712400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1475500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1366500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1284100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1058600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1050400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>937200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>803300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>809800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>771700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1159000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1089900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1039800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1072700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1007000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1092300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>998400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1021000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>962300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>949800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>910700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>911900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>915500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>395600</v>
+        <v>79800</v>
       </c>
       <c r="E47" s="3">
-        <v>406800</v>
+        <v>74300</v>
       </c>
       <c r="F47" s="3">
-        <v>427300</v>
+        <v>59600</v>
       </c>
       <c r="G47" s="3">
-        <v>514500</v>
+        <v>42700</v>
       </c>
       <c r="H47" s="3">
-        <v>702600</v>
+        <v>42900</v>
       </c>
       <c r="I47" s="3">
-        <v>801500</v>
+        <v>243400</v>
       </c>
       <c r="J47" s="3">
+        <v>309500</v>
+      </c>
+      <c r="K47" s="3">
         <v>732900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>682700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>700600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>639900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>772500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1002800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2229100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2823700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2474300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2509000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2465400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>410100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>472000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>512200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>512700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>462200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>422400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>457900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>451800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>381000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>324000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>286100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>211900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>205400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>182300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>343900</v>
+      </c>
+      <c r="E48" s="3">
         <v>320000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>325800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>330700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>323200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>322000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>289800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>281200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>273900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>264200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>260600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>271600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>242000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>247300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>250400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>258700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>261700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>269900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>279200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>284500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>330500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>336200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>337700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>297500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>296900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>301000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>302600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>272000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>266600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>264400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>254100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>261400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>254400</v>
+        <v>238000</v>
       </c>
       <c r="E49" s="3">
-        <v>258600</v>
+        <v>244900</v>
       </c>
       <c r="F49" s="3">
-        <v>263000</v>
+        <v>249100</v>
       </c>
       <c r="G49" s="3">
-        <v>267000</v>
+        <v>253500</v>
       </c>
       <c r="H49" s="3">
-        <v>271400</v>
+        <v>257500</v>
       </c>
       <c r="I49" s="3">
-        <v>217300</v>
+        <v>261900</v>
       </c>
       <c r="J49" s="3">
+        <v>207800</v>
+      </c>
+      <c r="K49" s="3">
         <v>220600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>223700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>223100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>226500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>267800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>272400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>276900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>281400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>289400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>295600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>300600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>305700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>308200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>316800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>365100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>362400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>367500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>380900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>387800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>396300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>369400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>376700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>382500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>386900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>394600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>412900</v>
+        <v>327000</v>
       </c>
       <c r="E52" s="3">
-        <v>336500</v>
+        <v>331000</v>
       </c>
       <c r="F52" s="3">
-        <v>342000</v>
+        <v>335100</v>
       </c>
       <c r="G52" s="3">
-        <v>348700</v>
+        <v>340600</v>
       </c>
       <c r="H52" s="3">
-        <v>166000</v>
+        <v>345100</v>
       </c>
       <c r="I52" s="3">
-        <v>162000</v>
+        <v>162400</v>
       </c>
       <c r="J52" s="3">
+        <v>158500</v>
+      </c>
+      <c r="K52" s="3">
         <v>195900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>175900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>188500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>92400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>79100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>57600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>64500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>93000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>108600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>121400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>139600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>154000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>247900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>146400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>172700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>184100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>176400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>180300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>180100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>178300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>170100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>216300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>222300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>216100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>213300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3634100</v>
+      </c>
+      <c r="E54" s="3">
         <v>3674700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3641000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3990400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3951200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3766900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3552900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3235800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3068600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2852000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2585900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2675200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2633400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3868200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4385900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3934400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3997500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3947000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2308000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2331800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2345700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2459400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2353300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2356100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2314300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2341600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5230,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>154600</v>
+      </c>
+      <c r="E57" s="3">
         <v>151700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>142900</v>
-      </c>
-      <c r="F57" s="3">
-        <v>131900</v>
       </c>
       <c r="G57" s="3">
         <v>131900</v>
       </c>
       <c r="H57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="I57" s="3">
         <v>135900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>120100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>109600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>132800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>142200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>154500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>123300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>133000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>130500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>136400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>100800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>117000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>107900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>103500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>88200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>107100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>113800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>126500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>106300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>118000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>125200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>123700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>104900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>112300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>104400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>96200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>89300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>15300</v>
       </c>
       <c r="E58" s="3">
-        <v>100</v>
+        <v>15300</v>
       </c>
       <c r="F58" s="3">
         <v>100</v>
       </c>
       <c r="G58" s="3">
+        <v>19900</v>
+      </c>
+      <c r="H58" s="3">
         <v>300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>11200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>10800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>11200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>10800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>14000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>14700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>17100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>16900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>15400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>102800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>58600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>53600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>64300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1669100</v>
+        <v>1552300</v>
       </c>
       <c r="E59" s="3">
-        <v>1722000</v>
+        <v>1556400</v>
       </c>
       <c r="F59" s="3">
-        <v>1933100</v>
+        <v>1633400</v>
       </c>
       <c r="G59" s="3">
-        <v>1955700</v>
+        <v>1793100</v>
       </c>
       <c r="H59" s="3">
-        <v>1839100</v>
+        <v>1829500</v>
       </c>
       <c r="I59" s="3">
-        <v>1746400</v>
+        <v>1714200</v>
       </c>
       <c r="J59" s="3">
+        <v>1651500</v>
+      </c>
+      <c r="K59" s="3">
         <v>1538800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1311900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1026400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>627000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>590600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>418700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>391700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>454700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>405500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>434500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>524500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>684200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>950700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>866600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>789700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>588300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>586600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>492500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>442200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>401100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>407900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>316500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>293800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>279000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>312100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1820600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1820800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1864900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2065100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2087800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1975400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1867500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1649100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1445200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1169900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>783000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>715000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>562900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>533000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>602300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>517000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>565600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>646800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>802300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>935800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>990800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>920400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>730200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>696800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>613500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>570900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>528200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>514900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>531600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>456800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>428700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>465800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>238600</v>
+        <v>329300</v>
       </c>
       <c r="E61" s="3">
-        <v>254900</v>
+        <v>293600</v>
       </c>
       <c r="F61" s="3">
-        <v>361300</v>
+        <v>313200</v>
       </c>
       <c r="G61" s="3">
-        <v>361500</v>
+        <v>425700</v>
       </c>
       <c r="H61" s="3">
-        <v>364100</v>
+        <v>421700</v>
       </c>
       <c r="I61" s="3">
-        <v>366800</v>
+        <v>425800</v>
       </c>
       <c r="J61" s="3">
+        <v>409600</v>
+      </c>
+      <c r="K61" s="3">
         <v>373500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>388000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>445000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>634200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>753400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1069500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2399800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2898700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2560500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2594600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2528400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>694000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>471800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>555400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>595300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>622900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>658400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>659500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>672800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>643900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>589100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>338300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>394400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>409200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>330100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>501600</v>
+        <v>322200</v>
       </c>
       <c r="E62" s="3">
-        <v>519900</v>
+        <v>377700</v>
       </c>
       <c r="F62" s="3">
-        <v>558600</v>
+        <v>398200</v>
       </c>
       <c r="G62" s="3">
-        <v>567000</v>
+        <v>429600</v>
       </c>
       <c r="H62" s="3">
-        <v>511500</v>
+        <v>417100</v>
       </c>
       <c r="I62" s="3">
-        <v>498700</v>
+        <v>343800</v>
       </c>
       <c r="J62" s="3">
+        <v>319900</v>
+      </c>
+      <c r="K62" s="3">
         <v>411700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>487700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>513600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>514500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>537800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>396000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>342900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>292100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>317600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>367700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>342500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>382100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>457500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>281800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>421300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>469900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>529300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>506800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>542600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>489900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>493000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>481500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>468200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>476900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>467000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2606500</v>
+        <v>2550400</v>
       </c>
       <c r="E66" s="3">
-        <v>2687300</v>
+        <v>2561000</v>
       </c>
       <c r="F66" s="3">
-        <v>3031800</v>
+        <v>2639700</v>
       </c>
       <c r="G66" s="3">
-        <v>3065700</v>
+        <v>2985000</v>
       </c>
       <c r="H66" s="3">
-        <v>2900600</v>
+        <v>3016300</v>
       </c>
       <c r="I66" s="3">
-        <v>2734200</v>
+        <v>2851000</v>
       </c>
       <c r="J66" s="3">
+        <v>2733000</v>
+      </c>
+      <c r="K66" s="3">
         <v>2435600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2322100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2129500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1932700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2011900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2033600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3280900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3798100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3399700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3532400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3522000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1882500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1868900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1831800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1940700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1826700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1867300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1780800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1793000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,31 +6722,34 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -6652,8 +6826,11 @@
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1042900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1068300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>953700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>958600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>885500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>866300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>818600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>800200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>746500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>722500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>653200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>663300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>599800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>587400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>587800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>534700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>465100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>425100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>425500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>462800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>513900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>518800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>526600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>488800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>533600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>548600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>536900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>546100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>663200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>595700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>589000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>548700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E81" s="3">
         <v>116300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>41300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>25600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>59200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>73000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>36300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>92100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>28900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>22300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>27200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>53000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>98000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-86000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-35500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>21100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>15700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-30500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>13000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>11300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>14400</v>
+        <v>10300</v>
       </c>
       <c r="E83" s="3">
-        <v>14400</v>
+        <v>9600</v>
       </c>
       <c r="F83" s="3">
-        <v>15100</v>
+        <v>9400</v>
       </c>
       <c r="G83" s="3">
-        <v>14700</v>
+        <v>9800</v>
       </c>
       <c r="H83" s="3">
-        <v>13800</v>
+        <v>9100</v>
       </c>
       <c r="I83" s="3">
-        <v>12900</v>
+        <v>9600</v>
       </c>
       <c r="J83" s="3">
+        <v>9900</v>
+      </c>
+      <c r="K83" s="3">
         <v>13500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>12700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>13300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>14200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>15300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>15100</v>
       </c>
       <c r="Q83" s="3">
         <v>15100</v>
       </c>
       <c r="R83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="S83" s="3">
         <v>16600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>16300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>16200</v>
       </c>
       <c r="U83" s="3">
         <v>16200</v>
       </c>
       <c r="V83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="W83" s="3">
         <v>18500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>18400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>17900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>21600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>24100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E89" s="3">
         <v>69000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>197500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>66200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-48200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-151700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>42300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-87600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-13300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>29500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>36400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>93600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>164700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>57200</v>
-      </c>
-      <c r="W89" s="3">
-        <v>8900</v>
       </c>
       <c r="X89" s="3">
         <v>8900</v>
       </c>
       <c r="Y89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="Z89" s="3">
         <v>36700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>15100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>42800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>15500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>81000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>73900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-12800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-17400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-7000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-10700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53700</v>
+      </c>
+      <c r="E94" s="3">
         <v>16800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>39100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>26500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-24800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>10100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-154000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-90900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-58300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>35500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>176700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1125400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>569100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-354000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>111200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-8400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-69300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-10000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-117900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-77800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-59500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-67200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8679,16 +8913,19 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-89800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-103300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-367300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-21900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>168200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>45500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>272700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>115200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>175000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>152800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-145900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-552100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>411800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-143100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1621100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>48200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-93300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>89700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-80700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>87700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>108800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>40000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>127600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>45600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>46200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="E101" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F101" s="3">
+        <v>100</v>
+      </c>
+      <c r="G101" s="3">
+        <v>300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>900</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K101" s="3">
+        <v>300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>900</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P101" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="I101" s="3">
-        <v>100</v>
-      </c>
-      <c r="J101" s="3">
-        <v>300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>900</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="O101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>-800</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="S101" s="3">
-        <v>100</v>
       </c>
       <c r="T101" s="3">
         <v>100</v>
       </c>
       <c r="U101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>500</v>
-      </c>
-      <c r="AH101" s="3">
-        <v>-400</v>
       </c>
       <c r="AI101" s="3">
         <v>-400</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-40700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-131300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>209000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>70600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-127100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>159900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-123900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>192600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-91600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>24100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>64500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>34200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-288700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>256400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>36200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-94000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-20200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-120900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>43800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-34800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>123900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>121800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-39100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>497900</v>
+      </c>
+      <c r="E8" s="3">
         <v>520400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>533200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>476300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>466900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>492300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>500900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>445400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>422600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>425700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>441400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>405700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>431900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>392100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>386400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>314500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>337300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>330300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>294400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>347200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>342400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>371100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>385700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>355800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>378600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>405300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>434400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>366200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>335300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>355000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>358400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>323300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>317700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>279400</v>
+      </c>
+      <c r="E9" s="3">
         <v>295600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>303200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>274200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>269000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>283300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>289400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>261300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>266300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>273700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>288800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>268200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>292000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>252800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>250600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>208700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>227300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>220600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>196200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>220800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>224600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>236500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>252500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>238500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>264200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>284500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>299200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>261800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>234500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>247400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>246400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>227300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>226700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>201600</v>
+      </c>
+      <c r="E10" s="3">
         <v>195100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>204600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>177500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>168100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>149600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>189900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>162500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>156300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>152000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>152600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>137500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>139900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>139300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>135800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>105800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>110000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>109700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>98200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>126400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>117800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>134600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>133200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>117300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>114400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>120800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>135200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>104400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>100800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>107600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>112000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>96000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>91000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,47 +1377,50 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-8700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-85200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1409,37 +1428,37 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-8100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1100</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-8300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>24900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>8100</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1447,12 +1466,12 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>2000</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1460,40 +1479,43 @@
         <v>0</v>
       </c>
       <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E15" s="3">
         <v>15000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>14400</v>
       </c>
       <c r="F15" s="3">
         <v>14400</v>
       </c>
       <c r="G15" s="3">
+        <v>14400</v>
+      </c>
+      <c r="H15" s="3">
         <v>15100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>14700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>13800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>12900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1569,8 +1591,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>431100</v>
+      </c>
+      <c r="E17" s="3">
         <v>462600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>468300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>434200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>427500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>467600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>447300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>397800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>380100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>374400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>307100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>355500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>373000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>332600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>322800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>241700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>291200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>276800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>280600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>322600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>305200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>347800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>361800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>330400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>361900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>376400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>390700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>351900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>326100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>330400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>325700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>318900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>334700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E18" s="3">
         <v>57800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>64900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>42200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>24700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>53600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>47600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>42500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>51300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>134300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>50200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>58900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>59500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>63600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>72800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>46100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>53500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>37200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>23300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>23900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>25400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>28900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>43700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>24600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>32700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>4400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,528 +1882,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>57400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-27700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>16100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>4500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-23300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>51200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-18000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-12000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>30200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>36400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-14400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E21" s="3">
         <v>72700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>57400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>59900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>37000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>66400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>57700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>113400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>67600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>149100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>36600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>90400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>53100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>83200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>64600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>113800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>70800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>21500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>37600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>71800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>78200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>45000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>22800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>27400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>51100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>19100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>26100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>43300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>49700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>21000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>6900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>7700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>21600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>14100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>14200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>13500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>11900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>6300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>6200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E23" s="3">
         <v>53100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>45700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>42700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>43300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>84400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>45000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>129300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>16800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>67800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>60000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>41800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>88400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>45000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>39300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>45900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>19600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>18500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>26100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E24" s="3">
         <v>16200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-59000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>10900</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-15300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>14600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>17700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>39400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>27700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>13500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-16900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>13700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>14800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>24100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>10400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E26" s="3">
         <v>36900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>124900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>42700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>27900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>58600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>66700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>35800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>89900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>40200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>24800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>27200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>60300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-4900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>20500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>25600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>31100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>12000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E27" s="3">
         <v>36400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>116300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>41300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>25600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>59200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>73000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>36300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>92100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>28900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>22300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>27100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>53000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>82900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>34400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-36600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>24000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>19800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>13000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>11300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2821,59 +2881,59 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>100</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>15100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>1100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-1300</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-49400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-47600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-26500</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-4100</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2884,14 +2944,17 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-57400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>27700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-16100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-4500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>23300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-51200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>18000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>12000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-30200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-36400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>14400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>23100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>12200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>13900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E33" s="3">
         <v>36400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>116300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>41300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>25600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>59200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>73000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>36300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>92100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>28900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>22300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>27200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>53000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>98000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-86000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-35500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>21100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>15700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>13000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>11300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E35" s="3">
         <v>36400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>116300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>41300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>25600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>59200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>73000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>36300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>92100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>28900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>22300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>27200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>53000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>98000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-86000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-35500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>21100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>15700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>13000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>11300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>404400</v>
+      </c>
+      <c r="E41" s="3">
         <v>388100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>428800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>446700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>577900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>562100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>353200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>305100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>234400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>361500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>201600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>201400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>325400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>224300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>200200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>135800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>141300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>107100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>395800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>137900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>112100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>206200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>212300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>334900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>289000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>324800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>322800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>418800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>296100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>337800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>382300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>450100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3851,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S42" s="3">
         <v>100</v>
@@ -3860,783 +3949,807 @@
         <v>100</v>
       </c>
       <c r="U42" s="3">
+        <v>100</v>
+      </c>
+      <c r="V42" s="3">
         <v>200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3900</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>15100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>58300</v>
-      </c>
-      <c r="AF42" s="3">
-        <v>46200</v>
       </c>
       <c r="AG42" s="3">
         <v>46200</v>
       </c>
       <c r="AH42" s="3">
+        <v>46200</v>
+      </c>
+      <c r="AI42" s="3">
         <v>60000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>53700</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1059200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1024300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>932200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>925000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>935600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>906900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>946100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>830400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1328500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1102700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1022800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>846500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>726400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>710300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>616900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>529100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>472300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>479200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>488300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>580200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>720500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>725500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>661500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>575900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>551900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>496000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>491000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>421400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>371100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>431300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>358900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>300300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>254500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>195600</v>
+      </c>
+      <c r="E44" s="3">
         <v>210700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>205400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>204800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>202300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>214800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>224100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>220900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>214100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>210900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>212700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>197000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>184300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>169700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>157900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>151600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>137100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>149600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>143900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>153100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>148500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>160700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>163300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>166600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>158900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>164500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>158600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>160500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>142600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>140200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>131300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>129300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>119200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
       <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>121600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>45900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>51300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>56200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>58100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>39600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>32200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>29800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>82800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>50400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>78100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>45700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>42600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>42500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>37800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>36000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>36500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>39900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2443700</v>
+      </c>
+      <c r="E46" s="3">
         <v>2317900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2291800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2313200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2627400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2497900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2304900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2082200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1805200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1712400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1475500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1366500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1284100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1058600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1050400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>937200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>803300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>809800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>771700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1159000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1089900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1039800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1072700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1007000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1092300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>998400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1021000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>962300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>949800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>910700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>911900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>915500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E47" s="3">
         <v>79800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>74300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>42700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>243400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>309500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>732900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>682700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>700600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>639900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>772500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1002800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2229100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2823700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2474300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2509000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2465400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>410100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>472000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>512200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>512700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>462200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>422400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>457900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>451800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>381000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>324000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>286100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>211900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>205400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>182300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>342100</v>
+      </c>
+      <c r="E48" s="3">
         <v>343900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>320000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>325800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>330700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>323200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>322000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>289800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>281200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>273900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>264200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>260600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>271600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>242000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>247300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>250400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>258700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>261700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>269900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>279200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>284500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>330500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>336200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>337700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>297500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>296900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>301000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>302600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>272000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>266600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>264400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>254100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>261400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E49" s="3">
         <v>238000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>244900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>249100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>253500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>257500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>261900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>207800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>220600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>223700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>223100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>226500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>267800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>272400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>276900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>281400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>289400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>295600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>300600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>305700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>308200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>316800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>365100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>362400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>367500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>380900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>387800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>396300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>369400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>376700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>382500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>386900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>394600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E52" s="3">
         <v>327000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>331000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>335100</v>
       </c>
-      <c r="G52" s="3">
-        <v>340600</v>
-      </c>
       <c r="H52" s="3">
+        <v>340000</v>
+      </c>
+      <c r="I52" s="3">
         <v>345100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>162400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>158500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>195900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>175900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>188500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>92400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>79100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>57600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>64500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>93000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>108600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>121400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>139600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>154000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>247900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>146400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>172700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>184100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>176400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>180300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>180100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>178300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>170100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>216300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>222300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>216100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>213300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3580300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3634100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3674700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3641000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3990400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3951200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3766900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3552900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3235800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3068600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2852000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2585900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2675200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2633400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3868200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4385900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3934400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3997500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3947000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2308000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2331800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2345700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2459400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2353300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2356100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2314300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2341600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,632 +5360,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E57" s="3">
         <v>154600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>142900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>131900</v>
       </c>
       <c r="H57" s="3">
         <v>131900</v>
       </c>
       <c r="I57" s="3">
+        <v>131900</v>
+      </c>
+      <c r="J57" s="3">
         <v>135900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>120100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>109600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>132800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>142200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>154500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>123300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>133000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>130500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>136400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>100800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>117000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>107900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>103500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>88200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>107100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>113800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>126500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>106300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>118000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>125200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>123700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>104900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>112300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>104400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>96200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>89300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>15300</v>
+        <v>18900</v>
       </c>
       <c r="E58" s="3">
         <v>15300</v>
       </c>
       <c r="F58" s="3">
+        <v>15300</v>
+      </c>
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>19900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>10800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>11200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>14400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>14700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>17100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>16900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>15400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>102800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>58600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>53600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>64300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1567000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1552300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1556400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1633400</v>
       </c>
-      <c r="G59" s="3">
-        <v>1793100</v>
-      </c>
       <c r="H59" s="3">
+        <v>1806100</v>
+      </c>
+      <c r="I59" s="3">
         <v>1829500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1714200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1651500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1538800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1311900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1026400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>627000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>590600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>418700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>391700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>454700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>405500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>434500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>524500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>684200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>950700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>866600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>789700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>588300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>586600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>492500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>442200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>401100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>407900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>316500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>293800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>279000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>312100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1818400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1820600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1820800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1864900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2065100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2087800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1975400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1867500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1649100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1445200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1169900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>783000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>715000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>562900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>533000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>602300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>517000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>565600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>646800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>802300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>935800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>990800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>920400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>730200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>696800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>613500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>570900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>528200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>514900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>531600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>456800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>428700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>465800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>332800</v>
+      </c>
+      <c r="E61" s="3">
         <v>329300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>293600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>313200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>425700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>421700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>425800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>409600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>373500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>388000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>445000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>634200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>753400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1069500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2399800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2898700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2560500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2594600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2528400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>694000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>471800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>555400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>595300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>622900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>658400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>659500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>672800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>643900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>589100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>338300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>394400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>409200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>330100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>229200</v>
+      </c>
+      <c r="E62" s="3">
         <v>322200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>377700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>398200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>429600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>417100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>343800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>319900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>411700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>487700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>513600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>514500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>537800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>396000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>342900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>292100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>317600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>367700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>342500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>382100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>457500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>281800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>421300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>469900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>529300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>506800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>542600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>489900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>493000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>481500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>468200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>476900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>467000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2406800</v>
+      </c>
+      <c r="E66" s="3">
         <v>2550400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2561000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2639700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2985000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3016300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2851000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2733000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2435600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2322100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2129500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1932700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2011900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2033600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3280900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3798100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3399700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3532400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3522000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1882500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1868900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1831800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1940700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1826700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1867300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1780800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1793000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6751,8 +6924,8 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -6829,8 +7002,11 @@
       <c r="AJ72" s="3">
         <v>0</v>
       </c>
+      <c r="AK72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1132400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1042900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1068300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>953700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>958600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>885500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>866300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>818600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>800200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>746500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>722500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>653200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>663300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>599800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>587400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>587800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>534700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>465100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>425100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>425500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>462800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>513900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>518800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>526600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>488800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>533600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>548600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>536900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>546100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>663200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>595700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>589000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>548700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E81" s="3">
         <v>36400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>116300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>41300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>25600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>59200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>73000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>36300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>92100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>28900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>22300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>27200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>53000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>98000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-86000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-35500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>21100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>15700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-30500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>13000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>11300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E83" s="3">
         <v>10300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>9800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>9600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>9900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>13500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>13300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>14200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>15300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>15000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>15100</v>
       </c>
       <c r="R83" s="3">
         <v>15100</v>
       </c>
       <c r="S83" s="3">
+        <v>15100</v>
+      </c>
+      <c r="T83" s="3">
         <v>16600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>16300</v>
-      </c>
-      <c r="U83" s="3">
-        <v>16200</v>
       </c>
       <c r="V83" s="3">
         <v>16200</v>
       </c>
       <c r="W83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="X83" s="3">
         <v>18500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>18400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>17900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>17500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>21600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>19600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>18700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>18300</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>101800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>69000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>197500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>66200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-48200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-151700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>42300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-87600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-13300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>43900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>29500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>36400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>93600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>164700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>57200</v>
-      </c>
-      <c r="X89" s="3">
-        <v>8900</v>
       </c>
       <c r="Y89" s="3">
         <v>8900</v>
       </c>
       <c r="Z89" s="3">
+        <v>8900</v>
+      </c>
+      <c r="AA89" s="3">
         <v>36700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>15100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>42800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>15500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>81000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>73900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-37300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-12800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-17400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-10700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>108800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-53700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>16800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>39100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>26500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-24800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-154000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-90900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-58300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>35500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>176700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1125400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>569100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-354000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>111200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>1700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-8400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-69300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-117900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-77800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-59500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-67200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9052,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8846,8 +9079,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8916,16 +9149,19 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-85900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-89800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-103300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-367300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-21900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>168200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>45500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>272700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>115200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>175000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>152800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-145900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-552100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>411800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-143100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1621100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>48200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-93300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>89700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-80700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>87700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>108800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>40000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>127600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>45600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1500</v>
-      </c>
-      <c r="T101" s="3">
-        <v>100</v>
       </c>
       <c r="U101" s="3">
         <v>100</v>
       </c>
       <c r="V101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>500</v>
-      </c>
-      <c r="AI101" s="3">
-        <v>-400</v>
       </c>
       <c r="AJ101" s="3">
         <v>-400</v>
       </c>
+      <c r="AK101" s="3">
+        <v>-400</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-40700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-131300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>209000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>70600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-127100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>159900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-123900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>192600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-91600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>24100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>64500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>34200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-288700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>256400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>36200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-94000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-20200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-120900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>43800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>123900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>121800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-39100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SPLP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>SPLP</t>
   </si>
@@ -656,479 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>499200</v>
+      </c>
+      <c r="F8" s="3">
         <v>497900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>520400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>533200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>476300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>466900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>492300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>500900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>445400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>422600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>425700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>441400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>405700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>431900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>392100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>386400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>314500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>337300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>330300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>294400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>347200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>342400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>371100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>385700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>355800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>378600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>405300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>434400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>366200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>335300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>355000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>358400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>323300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>317700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>316800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>307800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>280500</v>
+      </c>
+      <c r="F9" s="3">
         <v>279400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>295600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>303200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>274200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>269000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>283300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>289400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>261300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>266300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>273700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>288800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>268200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>292000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>252800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>250600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>208700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>227300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>220600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>196200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>220800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>224600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>236500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>252500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>238500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>264200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>284500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>299200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>261800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>234500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>247400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>246400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>227300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>226700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>223100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>223500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>198200</v>
+      </c>
+      <c r="F10" s="3">
         <v>201600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>195100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>204600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>177500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>168100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>149600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>189900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>162500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>156300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>152000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>152600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>137500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>139900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>139300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>135800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>105800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>110000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>109700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>98200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>126400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>117800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>134600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>133200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>117300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>114400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>120800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>135200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>104400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>100800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>107600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>112000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>91000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>93700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1192,10 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1301,14 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,148 +1414,160 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-27100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F14" s="3">
         <v>6100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>-1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>-4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>-400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-8700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-85200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-8100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>1200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>24900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>8100</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>2000</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3">
         <v>30000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AM14" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>15500</v>
+        <v>15000</v>
       </c>
       <c r="E15" s="3">
         <v>15000</v>
       </c>
       <c r="F15" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G15" s="3">
+        <v>15000</v>
+      </c>
+      <c r="H15" s="3">
         <v>14400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>14400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>15100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>14700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>13800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>12900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1594,8 +1640,14 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1682,236 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>471700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>447200</v>
+      </c>
+      <c r="F17" s="3">
         <v>431100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>462600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>468300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>434200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>427500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>467600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>447300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>397800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>380100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>374400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>307100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>355500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>373000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>332600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>322800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>241700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>291200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>276800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>280600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>322600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>305200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>347800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>361800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>330400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>361900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>376400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>390700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>351900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>326100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>330400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>325700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>318900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>334700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>299100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F18" s="3">
         <v>66800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>57800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>64900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>42200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>39400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>24700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>53600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>47600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>42500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>51300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>134300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>50200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>58900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>59500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>63600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>72800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>46100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>53500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>24600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>37200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>23300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>23900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>25400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>16700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>28900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>43700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>14300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>9200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>24600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>32700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>-17000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>17700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,543 +1949,575 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="F20" s="3">
         <v>4500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>-5400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>2300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>57400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-27700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>16100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-21400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>4500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-23300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>51200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>1000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-8500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-18000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>30200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>36400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-14400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-12200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>-13900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>2900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>68000</v>
+      </c>
+      <c r="F21" s="3">
         <v>77800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>72700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>81100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>57400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>59900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>37000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>66400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>57700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>113400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>67600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>149100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>36600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>90400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>53100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>83200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>64600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>113800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>70800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>21500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>22900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>37600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>71800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>78200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>45000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>22800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>27400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>51100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>19100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>26100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>43300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>49700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>9900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>37600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3100</v>
+      </c>
+      <c r="F22" s="3">
         <v>2900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>2000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>2500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>5800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>6000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>15500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>9900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>6500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>7200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>8100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>8800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>9500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>11200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>12100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>21600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>14200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>14500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>14100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>14200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>13500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>11900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>9900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>10000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>6300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>6200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>5300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AL22" s="3">
         <v>4400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AM22" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>104500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F23" s="3">
         <v>53300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>53100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>66000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>45700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>42700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>26900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>43300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>39400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>84400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>45000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>129300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>16800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>67800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>31200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>60000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>41800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>88400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>45000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-5900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-5400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>3500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>39300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>45900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>13400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>19600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>-9500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>18500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>26100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>-18500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F24" s="3">
         <v>-21300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>16200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-59000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>10900</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-15300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>14600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>17700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>9200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>39400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>27700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>6400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>35400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>14600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>28100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>13500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-3400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-16900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>13700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>14800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>3000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>3500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>7600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>24100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>9900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>10400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>5600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2623,240 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>29100</v>
+      </c>
+      <c r="F26" s="3">
         <v>74600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>36900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>124900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>34800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>42700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>27900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>58600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>24800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>66700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>35800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>89900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>9200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>40200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>24800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>24600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>27200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>60300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>31500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-2000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>20500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>25600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>31100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>10400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-7800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>12000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-25700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>8600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>15700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>-9400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>-24100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F27" s="3">
         <v>74600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>36400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>116300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>34200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>41300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>25600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>59200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>24800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>73000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>36300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>92100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>28900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>22300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>27100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>53000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>82900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>34400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-36600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>23600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>24000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>19800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>13000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>7000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>11300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2962,14 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2884,62 +3006,62 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>100</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
         <v>15100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>1100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="X29" s="3">
         <v>-1300</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>-49400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>-47600</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-4100</v>
       </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2947,14 +3069,20 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM29" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3188,14 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3301,240 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>5400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-2300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-57400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>27700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-16100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>21400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-4500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>23300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-51200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-1000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>8500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>18000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-30200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>14400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>23100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>12200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>13900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E33" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F33" s="3">
         <v>74600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>36400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>116300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>34200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>41300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>25600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>59200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>24800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>73000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>36300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>92100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>28900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>22300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>27200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>53000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>98000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>35600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-86000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>21100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>15700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>13000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>7000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>11300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3640,245 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E35" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F35" s="3">
         <v>74600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>36400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>116300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>34200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>41300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>25600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>59200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>24800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>73000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>36300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>92100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>28900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>22300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>27200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>53000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>98000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>35600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-86000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>21100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>15700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>13000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>7000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>11300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3916,10 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3957,123 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>346500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>341700</v>
+      </c>
+      <c r="F41" s="3">
         <v>404400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>388100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>428800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>446700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>577900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>562100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>353200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>305100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>234400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>361500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>201600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>201400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>325400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>132700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>224300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>200200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>135800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>141300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>107100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>395800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>137900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>112100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>206200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>212300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>334900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>289000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>324800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>322800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>418800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>296100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>337800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>382300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>450100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>328300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3943,16 +4123,16 @@
         <v>0</v>
       </c>
       <c r="S42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U42" s="3">
         <v>100</v>
       </c>
       <c r="V42" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W42" s="3">
         <v>100</v>
@@ -3961,795 +4141,843 @@
         <v>200</v>
       </c>
       <c r="Y42" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1100</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>1400</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>1700</v>
       </c>
       <c r="AB42" s="3">
         <v>1400</v>
       </c>
       <c r="AC42" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD42" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AE42" s="3">
         <v>3200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AF42" s="3">
         <v>3900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AG42" s="3">
         <v>15100</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AH42" s="3">
         <v>58300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AI42" s="3">
         <v>46200</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AJ42" s="3">
         <v>46200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AK42" s="3">
         <v>60000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AL42" s="3">
         <v>53700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AM42" s="3">
         <v>67300</v>
       </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1176300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1117400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1059200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1024300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>932200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>925000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>935600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>906900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>946100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>830400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1328500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1102700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1022800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>846500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>726400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>710300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>616900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>529100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>472300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>479200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>488300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>580200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>720500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>725500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>661500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>575900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>551900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>496000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>491000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>421400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>371100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>431300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>358900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>300300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>254500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>286200</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>203100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>204400</v>
+      </c>
+      <c r="F44" s="3">
         <v>195600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>210700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>205400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>204800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>202300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>214800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>224100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>220900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>214100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>210900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>212700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>197000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>184300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>169700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>157900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>151600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>137100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>149600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>143900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>153100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>148500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>160700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>163300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>166600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>158900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>164500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>158600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>160500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>142600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>140200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>131300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>129300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>119200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>127600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3">
         <v>100</v>
       </c>
-      <c r="I45" s="3">
-        <v>0</v>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="K45" s="3">
+        <v>0</v>
+      </c>
+      <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>28200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>37300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>38400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>121600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>48000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>45900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>51300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>56200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>58100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>39600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>32200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>29800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>82800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>40400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>40300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>50400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>78100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>45700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>42600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>42500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>37800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>36000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>36500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>39900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>38100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>38900</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2434100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2280600</v>
+      </c>
+      <c r="F46" s="3">
         <v>2443700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2317900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2291800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2313200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>2627400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>2497900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>2304900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>2082200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1805200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1712400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1475500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1366500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1284100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1058600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1050400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>937200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>803300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>809800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>771700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1159000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1089900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1039800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1072700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1007000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1092300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>998400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1021000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>962300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1028600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>949800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>910700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>911900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>915500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>848300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>187100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>154400</v>
+      </c>
+      <c r="F47" s="3">
         <v>85900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>79800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>74300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>59600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>42700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>42900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>243400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>309500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>732900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>682700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>700600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>639900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>772500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1002800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>2229100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>2823700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>2474300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>2509000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>2465400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>410100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>472000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>512200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>512700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>462200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>422400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>457900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AF47" s="3">
         <v>451800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AG47" s="3">
         <v>381000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AH47" s="3">
         <v>324000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AI47" s="3">
         <v>286100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AJ47" s="3">
         <v>211900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AK47" s="3">
         <v>205400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AL47" s="3">
         <v>182300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AM47" s="3">
         <v>190000</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>349000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>337500</v>
+      </c>
+      <c r="F48" s="3">
         <v>342100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>343900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>320000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>325800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>330700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>323200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>322000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>289800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>281200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>273900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>264200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>260600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>271600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>242000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>247300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>250400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>258700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>261700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>269900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>279200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>284500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>330500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>336200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>337700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>297500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>296900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>301000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>302600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>272000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>266600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>264400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>254100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>261400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>226200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>229700</v>
+      </c>
+      <c r="F49" s="3">
         <v>233500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>238000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>244900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>249100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>253500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>257500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>261900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>207800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>220600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>223700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>223100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>226500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>267800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>272400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>276900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>281400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>289400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>295600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>300600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>305700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>308200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>316800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>365100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>362400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>367500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>380900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>387800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>396300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>369400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>376700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>382500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>386900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>394600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>427100</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +5083,14 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5196,127 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>196700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>155700</v>
+      </c>
+      <c r="F52" s="3">
         <v>154200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>327000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>331000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>335100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>340000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>345100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>162400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>158500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>195900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>175900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>188500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>92400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>79100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>57600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>64500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>93000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>108600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>121400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>139600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>154000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>247900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>146400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>172700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>184100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>176400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>180300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>180100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>178300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>170100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>216300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>222300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>216100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>213300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>204200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5422,127 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3646300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3506800</v>
+      </c>
+      <c r="F54" s="3">
         <v>3580300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>3634100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>3674700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3641000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>3990400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>3951200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>3766900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>3552900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>3235800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>3068600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2852000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2585900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2675200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2633400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>3868200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>4385900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>3934400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>3997500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>3947000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2308000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2331800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2345700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2459400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2353300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2356100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2314300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2341600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2220500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>2164000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>2095600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1991800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1974400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1967100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1933600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5580,10 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,162 +5621,170 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>154100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>153100</v>
+      </c>
+      <c r="F57" s="3">
         <v>131800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>154600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>151700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>142900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>131900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>131900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>135900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>120100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>109600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>132800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>142200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>154500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>123300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>133000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>130500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>136400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>100800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>117000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>107900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>103500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>88200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>107100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>113800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>126500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>106300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>118000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>125200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>123700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>104900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>112300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>104400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>96200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>89300</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>90700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>143800</v>
+      </c>
+      <c r="F58" s="3">
         <v>18900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>15300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>15300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>19900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>500</v>
-      </c>
-      <c r="N58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="O58" s="3">
-        <v>1500</v>
       </c>
       <c r="P58" s="3">
         <v>1200</v>
       </c>
       <c r="Q58" s="3">
-        <v>11200</v>
+        <v>1500</v>
       </c>
       <c r="R58" s="3">
-        <v>10800</v>
+        <v>1200</v>
       </c>
       <c r="S58" s="3">
         <v>11200</v>
@@ -5525,486 +5793,516 @@
         <v>10800</v>
       </c>
       <c r="U58" s="3">
+        <v>11200</v>
+      </c>
+      <c r="V58" s="3">
+        <v>10800</v>
+      </c>
+      <c r="W58" s="3">
         <v>14000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>14400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>14700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>30800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>17100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>16900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>15400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>3900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>3000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>3600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>3400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>2100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>102800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>58600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>53600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>64300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1541200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1486200</v>
+      </c>
+      <c r="F59" s="3">
         <v>1567000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1552300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1556400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1633400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1806100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1829500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1714200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1651500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1538800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1311900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1026400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>627000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>590600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>418700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>391700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>454700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>405500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>434500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>524500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>684200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>950700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>866600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>789700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>588300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>586600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>492500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>442200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>401100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>407900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>316500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>293800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>279000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>312100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>166200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1950900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1866900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1818400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1820600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1820800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1864900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2065100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2087800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1975400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1867500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1649100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1445200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1169900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>783000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>715000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>562900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>533000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>602300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>517000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>565600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>646800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>802300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>935800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>990800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>920400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>730200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>696800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>613500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>570900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>528200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>514900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>531600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>456800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>428700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>465800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>171100</v>
+      </c>
+      <c r="F61" s="3">
         <v>332800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>329300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>293600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>313200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>425700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>421700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>425800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>409600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>373500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>388000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>445000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>634200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>753400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1069500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>2399800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2898700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2560500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>2594600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>2528400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>694000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>471800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>555400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>595300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>622900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>658400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>659500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>672800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>643900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>589100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>338300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>394400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>409200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>330100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>418100</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>293800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>277900</v>
+      </c>
+      <c r="F62" s="3">
         <v>229200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>322200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>377700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>398200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>429600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>417100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>343800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>319900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>411700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>487700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>513600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>514500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>537800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>396000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>342900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>292100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>317600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>367700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>342500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>382100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>457500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>281800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>421300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>469900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>529300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>506800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>542600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>489900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>493000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>481500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>468200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>476900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>467000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>500900</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6408,14 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6521,14 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6634,127 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2396100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2336100</v>
+      </c>
+      <c r="F66" s="3">
         <v>2406800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2550400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>2561000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>2639700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>2985000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3016300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2851000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2733000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>2435600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>2322100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2129500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1932700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>2011900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>2033600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>3280900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>3798100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>3399700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>3532400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>3522000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1882500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1868900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1831800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1940700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1826700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1867300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1780800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1793000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1683600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1617900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1432400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1396100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1385400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1418400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1348000</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6792,10 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6901,14 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +7014,14 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +7127,14 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,8 +7240,14 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6927,11 +7275,11 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
-      </c>
-      <c r="M72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N72" s="3">
         <v>0</v>
@@ -7005,8 +7353,14 @@
       <c r="AK72" s="3">
         <v>0</v>
       </c>
+      <c r="AL72" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7466,14 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7579,14 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7692,127 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1249900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1170400</v>
+      </c>
+      <c r="F76" s="3">
         <v>1132400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1042900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1068300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>953700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>958600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>885500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>866300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>818600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>800200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>746500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>722500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>653200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>663300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>599800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>587400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>587800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>534700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>465100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>425100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>425500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>462800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>513900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>518800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>526600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>488800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>533600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>548600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>536900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>546100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>663200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>595700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>589000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>548700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>585600</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7918,245 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>76900</v>
+      </c>
+      <c r="E81" s="3">
+        <v>29000</v>
+      </c>
+      <c r="F81" s="3">
         <v>74600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>36400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>116300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>34200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>41300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>25600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>59200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>24800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>73000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>36300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>92100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>28900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>22300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>27200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>53000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>98000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>35600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-86000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>21100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>15700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-30500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>13000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-9100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-14200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>7000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>11300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>-15400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +8194,123 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F83" s="3">
         <v>10800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>10300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>9600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>9400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>9800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>9100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>9900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>13500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>13300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>14200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>15300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>15000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>15100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>15100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>16600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>16300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>16200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>16200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>18500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>18400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>17900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>17500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>20400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>21600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>19600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>18700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>17700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>18500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>17400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>18300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>24100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>19200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8416,14 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8529,14 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8642,14 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8755,14 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8868,127 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>23700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>200400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>101800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>69000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>197500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>9500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>66200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-48200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-151700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>42300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-87600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-13300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>18800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>43900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>7900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>7200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>29500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>36400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>93600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>164700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>57200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>8900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>8900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>36700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>15100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>42800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>15500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-20700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>81000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-30800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>-51300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>73900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +9026,123 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-9300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-37300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-8300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-10100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-14800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-13100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-12800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-17400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-11700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-7700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-5600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-9000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-4900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-4500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-7000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-13500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-10000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-12000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-16800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-12900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-16100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-17800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-49600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-7300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9248,14 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9361,127 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-174600</v>
+      </c>
+      <c r="F94" s="3">
         <v>108800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-53700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>16800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>39100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>26500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-24800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>10100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-154000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-90900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-58300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-62800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>176700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>1125400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>569100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-354000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>111200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>1700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-2003500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-8400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-69300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-117900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-77800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-59500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-67200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-121400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-118400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-85000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-56200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>2700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-106700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,8 +9519,10 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9082,11 +9550,11 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9152,16 +9620,22 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-3900</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9741,14 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9854,14 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9967,349 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-85900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-89800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-103300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-367300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-21900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>168200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>45500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>272700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>115200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>175000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>152800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-145900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1262000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-552100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>411800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-143100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-4000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>1621100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>100200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>48200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-93300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>89700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-80700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>87700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-9900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>108800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>40000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>127600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>45600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-13900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>46200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>49900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>1600</v>
+        <v>-400</v>
       </c>
       <c r="E101" s="3">
         <v>-600</v>
       </c>
       <c r="F101" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H101" s="3">
         <v>-1200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-1500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>100</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
       </c>
       <c r="X101" s="3">
         <v>100</v>
       </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>-400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-62700</v>
+      </c>
+      <c r="F102" s="3">
         <v>16300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-40700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-17900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-131300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>15800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>209000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>48100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>70600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-127100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>159900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-123900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>192600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-91600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>24100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>64500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-4000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>34200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-288700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>256400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>36200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-94000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-120900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>43800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-34800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>2400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-98500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>123900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-44100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-66900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>121800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-39100</v>
       </c>
     </row>
